--- a/checklist_forms/028_holiday_village_display_setup_checklist--checklist_forms.xlsx
+++ b/checklist_forms/028_holiday_village_display_setup_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HOLIDAY VILLAGE DISPLAY SETUP CHECKLIST</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Holiday Village Display Setup Checklist</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Check each section carefully to ensure the display is ready for holiday season.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>holiday_village_display_details</t>
+          <t>installation_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HOLIDAY VILLAGE DISPLAY DETAILS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the installation location?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter the specific location of the holiday village display.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,59 +579,71 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INSTALLATION LOCATION</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Installation Location</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Choose the correct location for the holiday village display.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>installation_date</t>
+          <t>safety_check_list</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INSTALLATION DATE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Is there a safety check list available?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Check if the holiday village display has a safety check list.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>safety_check_list</t>
+          <t>safety_check_result</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAFETY CHECK LIST</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the safety check result?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter the result of the safety check.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +655,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>safety_check_result</t>
+          <t>display_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAFETY CHECK RESULT</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the display type?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Choose the correct display type for the holiday village display.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>display_type</t>
+          <t>display_location</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DISPLAY TYPE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the display location?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the specific location of the display.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>display_location</t>
+          <t>maintenance_check_list</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DISPLAY LOCATION</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Is there a maintenance check list?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Check if the holiday village display has a maintenance check list.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,197 +741,233 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DISPLAY DETAILS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What are the display details?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter the details of the holiday village display.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>maintenance_check_list</t>
+          <t>safety_check</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MAINTENANCE CHECK LIST</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Are there any issues with the safety checks?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Check if there are any issues with the safety checks.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>holiday_village</t>
+          <t>display_type_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Is the display type correct?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Check if the display type is correct.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>display_location</t>
+          <t>display_location_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>display_location</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Is the display location correct?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Check if the display location is correct.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>installation_date</t>
+          <t>holiday_village</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Is the holiday village name correct?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Check if the holiday village name is correct.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>installation_location</t>
+          <t>safety_check_result_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>installation_location</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Is the safety check result correct?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Check if the safety check result is correct.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>display_details</t>
+          <t>installation_date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>display_details</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Is the installation date correct?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Check if the installation date is correct.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>safety_check_list</t>
+          <t>installation_location_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>safety_check_list</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Is the installation location correct?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Check if the installation location is correct.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>safety_check_result</t>
+          <t>maintenance_check_list_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>safety_check_result</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Are there any issues with the maintenance checks?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Check if there are any issues with the maintenance checks.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,179 +979,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>display_type</t>
+          <t>display_details_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>display_type</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Are there any issues with the display details?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Check if there are any issues with the display details.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>display_location</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>display_location</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>safety_check_list</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>safety_check_list</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>safety_check_result</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>safety_check_result</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>holiday_village</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +1009,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,7 +1105,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>safety_check_result_choices</t>
+          <t>display_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>safety_check_result_choices</t>
+          <t>display_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1139,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>display_type_choices</t>
+          <t>maintenance_check_list_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1156,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>display_type_choices</t>
+          <t>maintenance_check_list_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1173,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>display_location_choices</t>
+          <t>safety_check_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1190,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>display_location_choices</t>
+          <t>safety_check_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1207,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>maintenance_check_list_choices</t>
+          <t>display_type_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1224,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>maintenance_check_list_choices</t>
+          <t>display_type_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1241,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>display_type_choices</t>
+          <t>display_location_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1258,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>display_type_choices</t>
+          <t>display_location_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1275,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>display_location_choices</t>
+          <t>holiday_village_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1292,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>display_location_choices</t>
+          <t>holiday_village_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1390,6 +1301,176 @@
         </is>
       </c>
       <c r="C17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>safety_check_result_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>safety_check_result_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>installation_date_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>installation_date_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>installation_location_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>installation_location_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>maintenance_check_list_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>maintenance_check_list_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>display_details_2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>display_details_2_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
